--- a/00_プロジェクト計画/【チーム演習】内部レビューチェックリスト.xlsx
+++ b/00_プロジェクト計画/【チーム演習】内部レビューチェックリスト.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734988B-13B4-4994-AEEF-02CEC27DE9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9817BA3-A3B6-41D2-988F-719498C6F4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22635" yWindow="-2190" windowWidth="20460" windowHeight="13200" tabRatio="775" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19290" yWindow="-4095" windowWidth="19380" windowHeight="10260" tabRatio="775" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)" sheetId="8" state="hidden" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="189">
   <si>
     <t>対象文書</t>
     <rPh sb="0" eb="2">
@@ -2587,6 +2587,69 @@
   <si>
     <t>出席者は妥当か。
 　　・PM、PL、要件定義書作成者は必須。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>榎本、筏谷、岩崎、小田、清水、山田</t>
+    <rPh sb="0" eb="2">
+      <t>エノモト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イカダ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タニ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イワサキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シミズ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヤマダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>WBS、フェーズ実績管理表、課題管理表</t>
+    <rPh sb="8" eb="13">
+      <t>ジッセキカンリヒョウ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>カダイカンリヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>（2026/06/24）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>榎本</t>
+    <rPh sb="0" eb="2">
+      <t>エノモト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>K2026-Z0011</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RFP、見積り決済シート</t>
+    <rPh sb="4" eb="6">
+      <t>ミツモ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケッサイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3899,215 +3962,205 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4117,6 +4170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4168,6 +4222,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4552,34 +4615,34 @@
   <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -4591,20 +4654,20 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="149" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -4620,18 +4683,18 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="139"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -4644,35 +4707,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -4682,14 +4745,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -4701,40 +4764,40 @@
       </c>
     </row>
     <row r="7" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="168"/>
+      <c r="B8" s="179"/>
       <c r="C8" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="169" t="s">
+      <c r="I8" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="49" t="s">
         <v>39</v>
       </c>
@@ -4743,42 +4806,42 @@
       </c>
     </row>
     <row r="9" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A9" s="163" t="s">
+      <c r="A9" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="164"/>
+      <c r="B9" s="132"/>
       <c r="C9" s="51">
         <v>1</v>
       </c>
-      <c r="D9" s="165" t="s">
+      <c r="D9" s="177" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
       <c r="K9" s="1"/>
       <c r="L9" s="27"/>
     </row>
     <row r="10" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="52">
         <v>2</v>
       </c>
-      <c r="D10" s="127" t="s">
+      <c r="D10" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
       <c r="K10" s="1"/>
       <c r="L10" s="28"/>
       <c r="M10" s="11" t="s">
@@ -4786,20 +4849,20 @@
       </c>
     </row>
     <row r="11" spans="1:18" s="11" customFormat="1" ht="63" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="52">
         <v>3</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
       <c r="K11" s="1"/>
       <c r="L11" s="28"/>
     </row>
@@ -4813,15 +4876,15 @@
       <c r="C12" s="52">
         <v>4</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="1"/>
       <c r="L12" s="28"/>
     </row>
@@ -4835,55 +4898,55 @@
       <c r="C13" s="53">
         <v>5</v>
       </c>
-      <c r="D13" s="177" t="s">
+      <c r="D13" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="179"/>
-      <c r="I13" s="177" t="s">
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="179"/>
+      <c r="J13" s="158"/>
       <c r="K13" s="17"/>
       <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:18" s="11" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="53">
         <v>6</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="177" t="s">
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="179"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="17"/>
       <c r="L14" s="30"/>
     </row>
     <row r="15" spans="1:18" s="11" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A15" s="172" t="s">
+      <c r="A15" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="173"/>
+      <c r="B15" s="181"/>
       <c r="C15" s="54"/>
-      <c r="D15" s="174"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="176"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="176"/>
+      <c r="D15" s="164"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="164"/>
+      <c r="J15" s="166"/>
       <c r="K15" s="5"/>
       <c r="L15" s="31"/>
     </row>
@@ -4971,34 +5034,34 @@
   <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -5010,21 +5073,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5040,21 +5103,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -5067,35 +5130,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -5105,14 +5168,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -5124,40 +5187,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="168"/>
+      <c r="B8" s="179"/>
       <c r="C8" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="215" t="s">
+      <c r="I8" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="49" t="s">
         <v>39</v>
       </c>
@@ -5199,24 +5262,24 @@
       <c r="Y9" s="37"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="186"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="196" t="s">
+      <c r="D10" s="192" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="196"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196" t="s">
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="192" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="196"/>
+      <c r="J10" s="192"/>
       <c r="K10" s="1"/>
       <c r="L10" s="32"/>
     </row>
@@ -5230,17 +5293,17 @@
       <c r="C11" s="3">
         <v>3</v>
       </c>
-      <c r="D11" s="196" t="s">
+      <c r="D11" s="192" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196" t="s">
+      <c r="E11" s="192"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="192"/>
+      <c r="H11" s="192"/>
+      <c r="I11" s="192" t="s">
         <v>159</v>
       </c>
-      <c r="J11" s="196"/>
+      <c r="J11" s="192"/>
       <c r="K11" s="1"/>
       <c r="L11" s="32"/>
     </row>
@@ -5254,32 +5317,32 @@
       <c r="C12" s="3">
         <v>4</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="192" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196" t="s">
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="192" t="s">
         <v>160</v>
       </c>
-      <c r="J12" s="196"/>
+      <c r="J12" s="192"/>
       <c r="K12" s="1"/>
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="186"/>
+      <c r="B13" s="163"/>
       <c r="C13" s="52"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="196"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
+      <c r="I13" s="192"/>
       <c r="J13" s="216"/>
       <c r="K13" s="1"/>
       <c r="L13" s="28"/>
@@ -5377,34 +5440,34 @@
   <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -5416,21 +5479,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5446,21 +5509,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -5473,35 +5536,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -5511,14 +5574,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -5530,40 +5593,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="168"/>
+      <c r="B8" s="179"/>
       <c r="C8" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="215" t="s">
+      <c r="I8" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="49" t="s">
         <v>39</v>
       </c>
@@ -5605,24 +5668,24 @@
       <c r="Y9" s="37"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="186"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="52">
         <v>2</v>
       </c>
-      <c r="D10" s="196" t="s">
+      <c r="D10" s="192" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="196"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196" t="s">
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="192" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="196"/>
+      <c r="J10" s="192"/>
       <c r="K10" s="1"/>
       <c r="L10" s="32"/>
     </row>
@@ -5636,15 +5699,15 @@
       <c r="C11" s="52">
         <v>3</v>
       </c>
-      <c r="D11" s="196" t="s">
+      <c r="D11" s="192" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196"/>
-      <c r="J11" s="196"/>
+      <c r="E11" s="192"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="192"/>
+      <c r="H11" s="192"/>
+      <c r="I11" s="192"/>
+      <c r="J11" s="192"/>
       <c r="K11" s="1"/>
       <c r="L11" s="32"/>
     </row>
@@ -5658,34 +5721,34 @@
       <c r="C12" s="52">
         <v>4</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="192" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
-      <c r="J12" s="196"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="192"/>
+      <c r="J12" s="192"/>
       <c r="K12" s="1"/>
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="186"/>
+      <c r="B13" s="163"/>
       <c r="C13" s="52">
         <v>5</v>
       </c>
-      <c r="D13" s="196" t="s">
+      <c r="D13" s="192" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="196"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
+      <c r="I13" s="192"/>
       <c r="J13" s="216"/>
       <c r="K13" s="1"/>
       <c r="L13" s="28"/>
@@ -5783,34 +5846,34 @@
   <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -5822,21 +5885,21 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5852,21 +5915,22 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
-        <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="139"/>
+      <c r="C3" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -5879,35 +5943,39 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -5917,14 +5985,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -5936,40 +6004,42 @@
       </c>
     </row>
     <row r="7" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="20" t="s">
+        <v>185</v>
+      </c>
       <c r="L7" s="116"/>
     </row>
     <row r="8" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="184"/>
+      <c r="B8" s="141"/>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="169" t="s">
+      <c r="I8" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
@@ -5978,64 +6048,68 @@
       </c>
     </row>
     <row r="9" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A9" s="163" t="s">
+      <c r="A9" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="164"/>
+      <c r="B9" s="132"/>
       <c r="C9" s="51">
         <v>1</v>
       </c>
-      <c r="D9" s="182" t="s">
+      <c r="D9" s="135" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="6"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="L9" s="115"/>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A10" s="180" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="181"/>
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="39.65" customHeight="1">
+      <c r="A10" s="133" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="134"/>
       <c r="C10" s="20">
         <v>2</v>
       </c>
-      <c r="D10" s="179" t="s">
+      <c r="D10" s="158" t="s">
         <v>150</v>
       </c>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127" t="s">
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160" t="s">
         <v>153</v>
       </c>
-      <c r="J10" s="177"/>
-      <c r="K10" s="6"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="L10" s="115"/>
     </row>
     <row r="11" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="180"/>
-      <c r="B11" s="181"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="134"/>
       <c r="C11" s="110">
         <v>3</v>
       </c>
-      <c r="D11" s="129" t="s">
+      <c r="D11" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129" t="s">
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="J11" s="129"/>
+      <c r="J11" s="145"/>
       <c r="K11" s="114"/>
       <c r="L11" s="115"/>
     </row>
@@ -6049,18 +6123,20 @@
       <c r="C12" s="52">
         <v>4</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127" t="s">
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160" t="s">
         <v>152</v>
       </c>
-      <c r="J12" s="127"/>
-      <c r="K12" s="6"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="L12" s="115"/>
     </row>
     <row r="13" spans="1:18" s="11" customFormat="1" ht="45" customHeight="1">
@@ -6073,118 +6149,128 @@
       <c r="C13" s="52">
         <v>5</v>
       </c>
-      <c r="D13" s="179" t="s">
+      <c r="D13" s="158" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="185"/>
-      <c r="F13" s="185"/>
-      <c r="G13" s="185"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="127" t="s">
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="177"/>
-      <c r="K13" s="6"/>
+      <c r="J13" s="161"/>
+      <c r="K13" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="L13" s="115"/>
     </row>
     <row r="14" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="186"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="52">
         <v>6</v>
       </c>
-      <c r="D14" s="127" t="s">
+      <c r="D14" s="160" t="s">
         <v>137</v>
       </c>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="6"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
+      <c r="K14" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="187"/>
+      <c r="B15" s="168"/>
       <c r="C15" s="20">
         <v>7</v>
       </c>
-      <c r="D15" s="127" t="s">
+      <c r="D15" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="1"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
+      <c r="K15" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="L15" s="115"/>
     </row>
     <row r="16" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="125"/>
-      <c r="B16" s="126"/>
+      <c r="A16" s="167"/>
+      <c r="B16" s="169"/>
       <c r="C16" s="52">
         <v>8</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127" t="s">
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="J16" s="127"/>
-      <c r="K16" s="1"/>
+      <c r="J16" s="160"/>
+      <c r="K16" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="L16" s="115"/>
     </row>
     <row r="17" spans="1:18" s="11" customFormat="1" ht="36" customHeight="1">
-      <c r="A17" s="123"/>
-      <c r="B17" s="124"/>
+      <c r="A17" s="162"/>
+      <c r="B17" s="170"/>
       <c r="C17" s="20">
         <v>9</v>
       </c>
-      <c r="D17" s="177" t="s">
+      <c r="D17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="179"/>
-      <c r="I17" s="177"/>
-      <c r="J17" s="179"/>
-      <c r="K17" s="1"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="158"/>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="L17" s="115"/>
       <c r="M17" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:18" s="11" customFormat="1" ht="156" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="186"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
       <c r="C18" s="110">
         <v>10</v>
       </c>
-      <c r="D18" s="188" t="s">
+      <c r="D18" s="172" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="189"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="190"/>
-      <c r="I18" s="188" t="s">
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="174"/>
+      <c r="I18" s="172" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="190"/>
+      <c r="J18" s="174"/>
       <c r="K18" s="111"/>
       <c r="L18" s="112"/>
       <c r="M18" s="11" t="s">
@@ -6192,36 +6278,36 @@
       </c>
     </row>
     <row r="19" spans="1:18" s="11" customFormat="1" ht="45" customHeight="1">
-      <c r="A19" s="123"/>
-      <c r="B19" s="124"/>
+      <c r="A19" s="162"/>
+      <c r="B19" s="170"/>
       <c r="C19" s="113">
         <v>11</v>
       </c>
-      <c r="D19" s="188" t="s">
+      <c r="D19" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="189"/>
-      <c r="H19" s="190"/>
-      <c r="I19" s="188" t="s">
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="J19" s="190"/>
+      <c r="J19" s="174"/>
       <c r="K19" s="111"/>
       <c r="L19" s="112"/>
     </row>
     <row r="20" spans="1:18" ht="30" customHeight="1" thickBot="1">
-      <c r="A20" s="191"/>
-      <c r="B20" s="192"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="176"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="174"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="176"/>
+      <c r="D20" s="164"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="166"/>
+      <c r="I20" s="164"/>
+      <c r="J20" s="166"/>
       <c r="K20" s="5"/>
       <c r="L20" s="31"/>
       <c r="P20" s="11"/>
@@ -6323,34 +6409,34 @@
   <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -6362,21 +6448,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -6392,21 +6478,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -6419,35 +6505,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -6457,14 +6543,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -6476,40 +6562,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="116"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="158"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="159" t="s">
+      <c r="D8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="159" t="s">
+      <c r="I8" s="186" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="162"/>
+      <c r="J8" s="188"/>
       <c r="K8" s="62" t="s">
         <v>39</v>
       </c>
@@ -6518,10 +6604,10 @@
       </c>
     </row>
     <row r="9" spans="1:25" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="182" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="193"/>
+      <c r="B9" s="183"/>
       <c r="C9" s="73"/>
       <c r="D9" s="74" t="s">
         <v>86</v>
@@ -6555,22 +6641,22 @@
       <c r="Y9" s="83"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="186"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="106">
         <v>1</v>
       </c>
-      <c r="D10" s="194" t="s">
+      <c r="D10" s="190" t="s">
         <v>145</v>
       </c>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="195"/>
-      <c r="J10" s="195"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
       <c r="K10" s="6"/>
       <c r="L10" s="115"/>
       <c r="M10" s="11" t="s">
@@ -6578,22 +6664,22 @@
       </c>
     </row>
     <row r="11" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="186"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="163"/>
       <c r="C11" s="110">
         <v>2</v>
       </c>
-      <c r="D11" s="131" t="s">
+      <c r="D11" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131" t="s">
+      <c r="E11" s="189"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="189"/>
+      <c r="I11" s="189" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="131"/>
+      <c r="J11" s="189"/>
       <c r="K11" s="111"/>
       <c r="L11" s="115"/>
     </row>
@@ -6607,17 +6693,17 @@
       <c r="C12" s="52">
         <v>3</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="192" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196" t="s">
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="192" t="s">
         <v>99</v>
       </c>
-      <c r="J12" s="196"/>
+      <c r="J12" s="192"/>
       <c r="K12" s="1"/>
       <c r="L12" s="115"/>
       <c r="M12" s="11" t="s">
@@ -6634,61 +6720,61 @@
       <c r="C13" s="52">
         <v>4</v>
       </c>
-      <c r="D13" s="177" t="s">
+      <c r="D13" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="179"/>
-      <c r="I13" s="177" t="s">
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="179"/>
+      <c r="J13" s="158"/>
       <c r="K13" s="1"/>
       <c r="L13" s="115"/>
     </row>
     <row r="14" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="186"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="52">
         <v>5</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="177" t="s">
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="161" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="179"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="1"/>
       <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="187"/>
+      <c r="B15" s="168"/>
       <c r="C15" s="52">
         <v>6</v>
       </c>
-      <c r="D15" s="177" t="s">
+      <c r="D15" s="161" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="177" t="s">
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="179"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="1"/>
       <c r="L15" s="115"/>
       <c r="M15" s="11" t="s">
@@ -6701,17 +6787,17 @@
       <c r="C16" s="52">
         <v>7</v>
       </c>
-      <c r="D16" s="177" t="s">
+      <c r="D16" s="161" t="s">
         <v>172</v>
       </c>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="177" t="s">
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="179"/>
+      <c r="J16" s="158"/>
       <c r="K16" s="17"/>
       <c r="L16" s="117"/>
       <c r="M16" s="11" t="s">
@@ -6724,15 +6810,15 @@
       <c r="C17" s="52">
         <v>8</v>
       </c>
-      <c r="D17" s="127" t="s">
+      <c r="D17" s="160" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160"/>
+      <c r="J17" s="160"/>
       <c r="K17" s="1"/>
       <c r="L17" s="112"/>
     </row>
@@ -6742,17 +6828,17 @@
       <c r="C18" s="110">
         <v>9</v>
       </c>
-      <c r="D18" s="129" t="s">
+      <c r="D18" s="145" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129" t="s">
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145" t="s">
         <v>167</v>
       </c>
-      <c r="J18" s="129"/>
+      <c r="J18" s="145"/>
       <c r="K18" s="111"/>
       <c r="L18" s="112"/>
     </row>
@@ -6857,34 +6943,34 @@
   <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -6896,21 +6982,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -6926,21 +7012,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -6953,35 +7039,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -6991,14 +7077,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -7010,40 +7096,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="116"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="158"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="159" t="s">
+      <c r="D8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="159" t="s">
+      <c r="I8" s="186" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="162"/>
+      <c r="J8" s="188"/>
       <c r="K8" s="62" t="s">
         <v>39</v>
       </c>
@@ -7052,10 +7138,10 @@
       </c>
     </row>
     <row r="9" spans="1:25" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="150"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="84"/>
       <c r="D9" s="74" t="s">
         <v>86</v>
@@ -7089,22 +7175,22 @@
       <c r="Y9" s="83"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="46.9" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="105">
         <v>1</v>
       </c>
-      <c r="D10" s="194" t="s">
+      <c r="D10" s="190" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="194"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="190"/>
+      <c r="J10" s="190"/>
       <c r="K10" s="6"/>
       <c r="L10" s="115"/>
       <c r="M10" s="11" t="s">
@@ -7115,22 +7201,22 @@
       <c r="R10" s="36"/>
     </row>
     <row r="11" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="120">
         <v>2</v>
       </c>
-      <c r="D11" s="129" t="s">
+      <c r="D11" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129" t="s">
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="129"/>
+      <c r="J11" s="145"/>
       <c r="K11" s="111"/>
       <c r="L11" s="115"/>
     </row>
@@ -7144,17 +7230,17 @@
       <c r="C12" s="105">
         <v>3</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="192" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="177" t="s">
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="161" t="s">
         <v>138</v>
       </c>
-      <c r="J12" s="179"/>
+      <c r="J12" s="158"/>
       <c r="K12" s="1"/>
       <c r="L12" s="115"/>
       <c r="M12" s="11" t="s">
@@ -7171,61 +7257,61 @@
       <c r="C13" s="105">
         <v>4</v>
       </c>
-      <c r="D13" s="177" t="s">
+      <c r="D13" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="179"/>
-      <c r="I13" s="177" t="s">
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="179"/>
+      <c r="J13" s="158"/>
       <c r="K13" s="1"/>
       <c r="L13" s="115"/>
     </row>
     <row r="14" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="105">
         <v>5</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="177" t="s">
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="161" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="179"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="1"/>
       <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="126"/>
+      <c r="B15" s="169"/>
       <c r="C15" s="105">
         <v>6</v>
       </c>
-      <c r="D15" s="177" t="s">
+      <c r="D15" s="161" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="177" t="s">
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="179"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="1"/>
       <c r="L15" s="115"/>
       <c r="M15" s="11" t="s">
@@ -7238,17 +7324,17 @@
       <c r="C16" s="105">
         <v>7</v>
       </c>
-      <c r="D16" s="177" t="s">
+      <c r="D16" s="161" t="s">
         <v>172</v>
       </c>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="177" t="s">
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="179"/>
+      <c r="J16" s="158"/>
       <c r="K16" s="17"/>
       <c r="L16" s="117"/>
       <c r="M16" s="11" t="s">
@@ -7261,17 +7347,17 @@
       <c r="C17" s="105">
         <v>8</v>
       </c>
-      <c r="D17" s="127" t="s">
+      <c r="D17" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127" t="s">
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160" t="s">
         <v>174</v>
       </c>
-      <c r="J17" s="127"/>
+      <c r="J17" s="160"/>
       <c r="K17" s="17"/>
       <c r="L17" s="117"/>
     </row>
@@ -7281,53 +7367,53 @@
       <c r="C18" s="105">
         <v>9</v>
       </c>
-      <c r="D18" s="127" t="s">
+      <c r="D18" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="160"/>
       <c r="K18" s="17"/>
       <c r="L18" s="117"/>
     </row>
     <row r="19" spans="1:18" s="11" customFormat="1" ht="45" customHeight="1">
-      <c r="A19" s="123"/>
-      <c r="B19" s="124"/>
+      <c r="A19" s="162"/>
+      <c r="B19" s="170"/>
       <c r="C19" s="120">
         <v>10</v>
       </c>
-      <c r="D19" s="129" t="s">
+      <c r="D19" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="129"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
       <c r="K19" s="111"/>
       <c r="L19" s="112"/>
     </row>
     <row r="20" spans="1:18" s="11" customFormat="1" ht="45" customHeight="1">
-      <c r="A20" s="123"/>
-      <c r="B20" s="124"/>
+      <c r="A20" s="162"/>
+      <c r="B20" s="170"/>
       <c r="C20" s="120">
         <v>11</v>
       </c>
-      <c r="D20" s="129" t="s">
+      <c r="D20" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129" t="s">
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145" t="s">
         <v>156</v>
       </c>
-      <c r="J20" s="129"/>
+      <c r="J20" s="145"/>
       <c r="K20" s="111"/>
       <c r="L20" s="112"/>
     </row>
@@ -7337,15 +7423,15 @@
       <c r="C21" s="120">
         <v>12</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="D21" s="145" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="198"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="194"/>
+      <c r="J21" s="195"/>
       <c r="K21" s="111"/>
       <c r="L21" s="112"/>
     </row>
@@ -7355,17 +7441,17 @@
       <c r="C22" s="121">
         <v>13</v>
       </c>
-      <c r="D22" s="202" t="s">
+      <c r="D22" s="199" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202" t="s">
+      <c r="E22" s="199"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199" t="s">
         <v>170</v>
       </c>
-      <c r="J22" s="202"/>
+      <c r="J22" s="199"/>
       <c r="K22" s="111"/>
       <c r="L22" s="112"/>
     </row>
@@ -7375,17 +7461,17 @@
       <c r="C23" s="121">
         <v>14</v>
       </c>
-      <c r="D23" s="129" t="s">
+      <c r="D23" s="145" t="s">
         <v>175</v>
       </c>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129" t="s">
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="145" t="s">
         <v>154</v>
       </c>
-      <c r="J23" s="129"/>
+      <c r="J23" s="145"/>
       <c r="K23" s="111"/>
       <c r="L23" s="112"/>
     </row>
@@ -7395,17 +7481,17 @@
       <c r="C24" s="121">
         <v>15</v>
       </c>
-      <c r="D24" s="129" t="s">
+      <c r="D24" s="145" t="s">
         <v>147</v>
       </c>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129" t="s">
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="145"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="145" t="s">
         <v>148</v>
       </c>
-      <c r="J24" s="129"/>
+      <c r="J24" s="145"/>
       <c r="K24" s="111"/>
       <c r="L24" s="112"/>
     </row>
@@ -7413,11 +7499,11 @@
       <c r="A25" s="41"/>
       <c r="B25" s="71"/>
       <c r="C25" s="46"/>
-      <c r="D25" s="199"/>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="201"/>
+      <c r="D25" s="196"/>
+      <c r="E25" s="197"/>
+      <c r="F25" s="197"/>
+      <c r="G25" s="197"/>
+      <c r="H25" s="198"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38"/>
       <c r="K25" s="46"/>
@@ -7519,34 +7605,34 @@
   <dimension ref="A1:Y25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -7558,21 +7644,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -7588,21 +7674,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -7615,35 +7701,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -7653,14 +7739,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -7672,40 +7758,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="158"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="159" t="s">
+      <c r="D8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="159" t="s">
+      <c r="I8" s="186" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="162"/>
+      <c r="J8" s="188"/>
       <c r="K8" s="62" t="s">
         <v>39</v>
       </c>
@@ -7714,10 +7800,10 @@
       </c>
     </row>
     <row r="9" spans="1:25" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="204"/>
+      <c r="B9" s="201"/>
       <c r="C9" s="85"/>
       <c r="D9" s="74" t="s">
         <v>86</v>
@@ -7751,42 +7837,42 @@
       <c r="Y9" s="83"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="34.5" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="205"/>
+      <c r="B10" s="202"/>
       <c r="C10" s="107">
         <v>1</v>
       </c>
-      <c r="D10" s="194" t="s">
+      <c r="D10" s="190" t="s">
         <v>176</v>
       </c>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="194"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="190"/>
+      <c r="J10" s="190"/>
       <c r="K10" s="6"/>
       <c r="L10" s="32"/>
     </row>
     <row r="11" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="205"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="202"/>
       <c r="C11" s="105">
         <v>2</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127" t="s">
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="127"/>
+      <c r="J11" s="160"/>
       <c r="K11" s="1"/>
       <c r="L11" s="32"/>
     </row>
@@ -7800,17 +7886,17 @@
       <c r="C12" s="105">
         <v>3</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127" t="s">
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160" t="s">
         <v>140</v>
       </c>
-      <c r="J12" s="127"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="1"/>
       <c r="L12" s="32"/>
     </row>
@@ -7824,17 +7910,17 @@
       <c r="C13" s="105">
         <v>4</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="160" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127" t="s">
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160" t="s">
         <v>141</v>
       </c>
-      <c r="J13" s="127"/>
+      <c r="J13" s="160"/>
       <c r="K13" s="1"/>
       <c r="L13" s="32"/>
       <c r="M13" s="11" t="s">
@@ -7842,24 +7928,24 @@
       </c>
     </row>
     <row r="14" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="205"/>
+      <c r="B14" s="202"/>
       <c r="C14" s="105">
         <v>5</v>
       </c>
-      <c r="D14" s="127" t="s">
+      <c r="D14" s="160" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127" t="s">
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="160" t="s">
         <v>174</v>
       </c>
-      <c r="J14" s="127"/>
+      <c r="J14" s="160"/>
       <c r="K14" s="1"/>
       <c r="L14" s="32"/>
       <c r="M14" s="34" t="s">
@@ -7867,24 +7953,24 @@
       </c>
     </row>
     <row r="15" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="203"/>
+      <c r="B15" s="200"/>
       <c r="C15" s="105">
         <v>6</v>
       </c>
-      <c r="D15" s="127" t="s">
+      <c r="D15" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127" t="s">
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="127"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="1"/>
       <c r="L15" s="32"/>
     </row>
@@ -7894,15 +7980,15 @@
       <c r="C16" s="105">
         <v>7</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="160" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
       <c r="K16" s="1"/>
       <c r="L16" s="32"/>
     </row>
@@ -7912,17 +7998,17 @@
       <c r="C17" s="105">
         <v>8</v>
       </c>
-      <c r="D17" s="127" t="s">
+      <c r="D17" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="140" t="s">
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="185"/>
+      <c r="J17" s="159"/>
       <c r="K17" s="1"/>
       <c r="L17" s="32"/>
     </row>
@@ -7932,17 +8018,17 @@
       <c r="C18" s="105">
         <v>9</v>
       </c>
-      <c r="D18" s="127" t="s">
+      <c r="D18" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="140" t="s">
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="185"/>
+      <c r="J18" s="159"/>
       <c r="K18" s="1"/>
       <c r="L18" s="32"/>
       <c r="M18" s="11" t="s">
@@ -7955,15 +8041,15 @@
       <c r="C19" s="105">
         <v>10</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
+      <c r="E19" s="160"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="160"/>
       <c r="K19" s="1"/>
       <c r="L19" s="32"/>
     </row>
@@ -7973,59 +8059,59 @@
       <c r="C20" s="105">
         <v>11</v>
       </c>
-      <c r="D20" s="127" t="s">
+      <c r="D20" s="160" t="s">
         <v>177</v>
       </c>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="127"/>
+      <c r="E20" s="160"/>
+      <c r="F20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
+      <c r="I20" s="160"/>
+      <c r="J20" s="160"/>
       <c r="K20" s="1"/>
       <c r="L20" s="28"/>
       <c r="M20" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="11" customFormat="1" ht="42.6" customHeight="1">
+    <row r="21" spans="1:18" s="11" customFormat="1" ht="42.65" customHeight="1">
       <c r="A21" s="56"/>
       <c r="B21" s="58"/>
       <c r="C21" s="105">
         <v>12</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="160" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127" t="s">
+      <c r="E21" s="160"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="160" t="s">
         <v>154</v>
       </c>
-      <c r="J21" s="127"/>
+      <c r="J21" s="160"/>
       <c r="K21" s="1"/>
       <c r="L21" s="28"/>
       <c r="M21" s="34"/>
     </row>
-    <row r="22" spans="1:18" ht="66.599999999999994" customHeight="1">
+    <row r="22" spans="1:18" ht="66.650000000000006" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="64"/>
       <c r="C22" s="105">
         <v>13</v>
       </c>
-      <c r="D22" s="127" t="s">
+      <c r="D22" s="160" t="s">
         <v>147</v>
       </c>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127" t="s">
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="160"/>
+      <c r="I22" s="160" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="127"/>
+      <c r="J22" s="160"/>
       <c r="K22" s="1"/>
       <c r="L22" s="28"/>
       <c r="P22" s="11"/>
@@ -8130,34 +8216,34 @@
   <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -8169,21 +8255,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -8199,21 +8285,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -8226,35 +8312,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -8264,14 +8350,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -8283,40 +8369,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="184"/>
+      <c r="B8" s="141"/>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="169" t="s">
+      <c r="I8" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
@@ -8325,10 +8411,10 @@
       </c>
     </row>
     <row r="9" spans="1:25" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="207" t="s">
+      <c r="A9" s="204" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="208"/>
+      <c r="B9" s="205"/>
       <c r="C9" s="86"/>
       <c r="D9" s="87" t="s">
         <v>86</v>
@@ -8362,42 +8448,42 @@
       <c r="Y9" s="83"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="7">
         <v>1</v>
       </c>
-      <c r="D10" s="194" t="s">
+      <c r="D10" s="190" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="206"/>
-      <c r="J10" s="206"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="203"/>
       <c r="K10" s="6"/>
       <c r="L10" s="32"/>
     </row>
     <row r="11" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="3">
         <v>2</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127" t="s">
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="127"/>
+      <c r="J11" s="160"/>
       <c r="K11" s="6"/>
       <c r="L11" s="32"/>
     </row>
@@ -8411,17 +8497,17 @@
       <c r="C12" s="3">
         <v>3</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127" t="s">
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="127"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="6"/>
       <c r="L12" s="32"/>
     </row>
@@ -8435,77 +8521,77 @@
       <c r="C13" s="3">
         <v>4</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="160" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127" t="s">
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="127"/>
+      <c r="J13" s="160"/>
       <c r="K13" s="6"/>
       <c r="L13" s="32"/>
     </row>
     <row r="14" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="8">
         <v>5</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="177"/>
-      <c r="J14" s="179"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="1"/>
       <c r="L14" s="32"/>
     </row>
     <row r="15" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="126"/>
+      <c r="B15" s="169"/>
       <c r="C15" s="3">
         <v>6</v>
       </c>
-      <c r="D15" s="177" t="s">
+      <c r="D15" s="161" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="177"/>
-      <c r="J15" s="179"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="1"/>
       <c r="L15" s="32"/>
     </row>
     <row r="16" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="123"/>
-      <c r="B16" s="124"/>
+      <c r="A16" s="162"/>
+      <c r="B16" s="170"/>
       <c r="C16" s="3">
         <v>7</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127" t="s">
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="127"/>
+      <c r="J16" s="160"/>
       <c r="K16" s="1"/>
       <c r="L16" s="32"/>
     </row>
@@ -8515,15 +8601,15 @@
       <c r="C17" s="3">
         <v>8</v>
       </c>
-      <c r="D17" s="127" t="s">
+      <c r="D17" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160"/>
+      <c r="J17" s="160"/>
       <c r="K17" s="17"/>
       <c r="L17" s="33"/>
       <c r="P17" s="11"/>
@@ -8535,15 +8621,15 @@
       <c r="C18" s="3">
         <v>9</v>
       </c>
-      <c r="D18" s="127" t="s">
+      <c r="D18" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="160"/>
       <c r="K18" s="1"/>
       <c r="L18" s="28"/>
       <c r="P18" s="11"/>
@@ -8555,15 +8641,15 @@
       <c r="C19" s="3">
         <v>10</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
+      <c r="E19" s="160"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="160"/>
       <c r="K19" s="1"/>
       <c r="L19" s="28"/>
       <c r="P19" s="11"/>
@@ -8574,13 +8660,13 @@
       <c r="A20" s="41"/>
       <c r="B20" s="39"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="209"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="209"/>
-      <c r="G20" s="209"/>
-      <c r="H20" s="209"/>
-      <c r="I20" s="209"/>
-      <c r="J20" s="209"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="206"/>
+      <c r="G20" s="206"/>
+      <c r="H20" s="206"/>
+      <c r="I20" s="206"/>
+      <c r="J20" s="206"/>
       <c r="K20" s="5"/>
       <c r="L20" s="31"/>
       <c r="P20" s="11"/>
@@ -8665,34 +8751,34 @@
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -8704,21 +8790,21 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -8734,21 +8820,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -8761,35 +8847,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -8799,14 +8885,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -8818,40 +8904,40 @@
       </c>
     </row>
     <row r="7" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="184"/>
+      <c r="B8" s="141"/>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="169" t="s">
+      <c r="I8" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
@@ -8860,10 +8946,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="163" t="s">
+      <c r="A9" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="164"/>
+      <c r="B9" s="132"/>
       <c r="C9" s="96"/>
       <c r="D9" s="97" t="s">
         <v>95</v>
@@ -8884,42 +8970,42 @@
       <c r="L9" s="95"/>
     </row>
     <row r="10" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="20">
         <v>1</v>
       </c>
-      <c r="D10" s="213" t="s">
+      <c r="D10" s="210" t="s">
         <v>181</v>
       </c>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="214"/>
-      <c r="J10" s="214"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="211"/>
+      <c r="J10" s="211"/>
       <c r="K10" s="6"/>
       <c r="L10" s="32"/>
     </row>
     <row r="11" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="52">
         <v>2</v>
       </c>
-      <c r="D11" s="140" t="s">
+      <c r="D11" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="214" t="s">
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="211" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="214"/>
+      <c r="J11" s="211"/>
       <c r="K11" s="6"/>
       <c r="L11" s="32"/>
     </row>
@@ -8933,17 +9019,17 @@
       <c r="C12" s="52">
         <v>3</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127" t="s">
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="127"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="6"/>
       <c r="L12" s="32"/>
     </row>
@@ -8957,55 +9043,55 @@
       <c r="C13" s="53">
         <v>4</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="160" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
       <c r="K13" s="6"/>
       <c r="L13" s="32"/>
     </row>
     <row r="14" spans="1:18" s="11" customFormat="1" ht="64.5" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="186"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="52">
         <v>5</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
       <c r="K14" s="6"/>
       <c r="L14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="30" customHeight="1">
-      <c r="A15" s="210" t="s">
+      <c r="A15" s="207" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="211"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="109">
         <v>6</v>
       </c>
-      <c r="D15" s="177" t="s">
+      <c r="D15" s="161" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="1"/>
       <c r="L15" s="32"/>
       <c r="P15" s="11"/>
@@ -9017,15 +9103,15 @@
       <c r="C16" s="109">
         <v>7</v>
       </c>
-      <c r="D16" s="177" t="s">
+      <c r="D16" s="161" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
       <c r="K16" s="1"/>
       <c r="L16" s="32"/>
       <c r="P16" s="11"/>
@@ -9036,13 +9122,13 @@
       <c r="A17" s="41"/>
       <c r="B17" s="39"/>
       <c r="C17" s="43"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="212"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="212"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
+      <c r="D17" s="209"/>
+      <c r="E17" s="209"/>
+      <c r="F17" s="209"/>
+      <c r="G17" s="209"/>
+      <c r="H17" s="209"/>
+      <c r="I17" s="209"/>
+      <c r="J17" s="209"/>
       <c r="K17" s="5"/>
       <c r="L17" s="31"/>
       <c r="P17" s="11"/>
@@ -9115,34 +9201,34 @@
   <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -9154,21 +9240,21 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -9184,21 +9270,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -9211,35 +9297,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -9249,14 +9335,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -9268,40 +9354,40 @@
       </c>
     </row>
     <row r="7" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:18" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="184"/>
+      <c r="B8" s="141"/>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="215" t="s">
+      <c r="I8" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="171"/>
+      <c r="J8" s="144"/>
       <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
@@ -9310,10 +9396,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="163" t="s">
+      <c r="A9" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="164"/>
+      <c r="B9" s="132"/>
       <c r="C9" s="96"/>
       <c r="D9" s="97" t="s">
         <v>95</v>
@@ -9338,42 +9424,42 @@
       </c>
     </row>
     <row r="10" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="20">
         <v>1</v>
       </c>
-      <c r="D10" s="213" t="s">
+      <c r="D10" s="210" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="214"/>
-      <c r="J10" s="214"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="211"/>
+      <c r="J10" s="211"/>
       <c r="K10" s="6"/>
       <c r="L10" s="32"/>
     </row>
     <row r="11" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="52">
         <v>2</v>
       </c>
-      <c r="D11" s="140" t="s">
+      <c r="D11" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="214" t="s">
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="211" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="214"/>
+      <c r="J11" s="211"/>
       <c r="K11" s="6"/>
       <c r="L11" s="32"/>
     </row>
@@ -9387,17 +9473,17 @@
       <c r="C12" s="52">
         <v>3</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127" t="s">
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="127"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="6"/>
       <c r="L12" s="32"/>
     </row>
@@ -9411,55 +9497,55 @@
       <c r="C13" s="53">
         <v>4</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
       <c r="K13" s="6"/>
       <c r="L13" s="32"/>
     </row>
     <row r="14" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="186"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="52">
         <v>5</v>
       </c>
-      <c r="D14" s="177" t="s">
+      <c r="D14" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="179"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
       <c r="K14" s="6"/>
       <c r="L14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="30" customHeight="1">
-      <c r="A15" s="210" t="s">
+      <c r="A15" s="207" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="211"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="52">
         <v>6</v>
       </c>
-      <c r="D15" s="177" t="s">
+      <c r="D15" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="6"/>
       <c r="L15" s="32"/>
       <c r="P15" s="11"/>
@@ -9471,15 +9557,15 @@
       <c r="C16" s="52">
         <v>7</v>
       </c>
-      <c r="D16" s="177" t="s">
+      <c r="D16" s="161" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
       <c r="K16" s="6"/>
       <c r="L16" s="32"/>
       <c r="P16" s="11"/>
@@ -9491,17 +9577,17 @@
       <c r="C17" s="52">
         <v>8</v>
       </c>
-      <c r="D17" s="177" t="s">
+      <c r="D17" s="161" t="s">
         <v>166</v>
       </c>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="179"/>
-      <c r="I17" s="127" t="s">
+      <c r="E17" s="171"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="160" t="s">
         <v>164</v>
       </c>
-      <c r="J17" s="127"/>
+      <c r="J17" s="160"/>
       <c r="K17" s="6"/>
       <c r="L17" s="32"/>
       <c r="P17" s="11"/>
@@ -9512,13 +9598,13 @@
       <c r="A18" s="41"/>
       <c r="B18" s="39"/>
       <c r="C18" s="43"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
+      <c r="D18" s="209"/>
+      <c r="E18" s="209"/>
+      <c r="F18" s="209"/>
+      <c r="G18" s="209"/>
+      <c r="H18" s="209"/>
+      <c r="I18" s="209"/>
+      <c r="J18" s="209"/>
       <c r="K18" s="5"/>
       <c r="L18" s="31"/>
       <c r="P18" s="11"/>
@@ -9596,34 +9682,34 @@
   <dimension ref="A1:Y25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="6.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="25.25" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="9" customWidth="1"/>
+    <col min="7" max="9" width="25.26953125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" style="9" customWidth="1"/>
     <col min="11" max="12" width="16" style="9" customWidth="1"/>
     <col min="13" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="e">
+      <c r="A1" s="146" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148"/>
       <c r="O1" s="12" t="s">
         <v>27</v>
       </c>
@@ -9635,21 +9721,21 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A2" s="135" t="str">
+      <c r="A2" s="149" t="str">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!A2:L2</f>
         <v>内部レビューチェックリスト　V 4.15.0</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="137"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="151"/>
       <c r="O2" s="12" t="s">
         <v>27</v>
       </c>
@@ -9665,21 +9751,21 @@
         <v>59</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="138">
+      <c r="C3" s="152">
         <f>'ﾚﾋﾞｭｰﾁｪｯｸﾘｽﾄ (提案)'!C3:D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="139"/>
+      <c r="D3" s="153"/>
       <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="155"/>
       <c r="O3" s="15" t="s">
         <v>28</v>
       </c>
@@ -9692,35 +9778,35 @@
         <v>0</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="157"/>
       <c r="P4" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="148"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
       <c r="P5" s="11" t="s">
         <v>76</v>
       </c>
@@ -9730,14 +9816,14 @@
         <v>12</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="130"/>
       <c r="K6" s="18" t="s">
         <v>54</v>
       </c>
@@ -9749,40 +9835,40 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A7" s="154" t="s">
+      <c r="A7" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="20"/>
       <c r="L7" s="116"/>
     </row>
     <row r="8" spans="1:25" s="11" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="158"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="159" t="s">
+      <c r="D8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="161" t="s">
+      <c r="I8" s="215" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="162"/>
+      <c r="J8" s="188"/>
       <c r="K8" s="62" t="s">
         <v>39</v>
       </c>
@@ -9791,10 +9877,10 @@
       </c>
     </row>
     <row r="9" spans="1:25" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="182" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="150"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="85"/>
       <c r="D9" s="74" t="s">
         <v>86</v>
@@ -9832,42 +9918,42 @@
       <c r="Y9" s="83"/>
     </row>
     <row r="10" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="107">
         <v>1</v>
       </c>
-      <c r="D10" s="130" t="s">
+      <c r="D10" s="214" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
+      <c r="E10" s="214"/>
+      <c r="F10" s="214"/>
+      <c r="G10" s="214"/>
+      <c r="H10" s="214"/>
+      <c r="I10" s="214"/>
+      <c r="J10" s="214"/>
       <c r="K10" s="1"/>
       <c r="L10" s="115"/>
     </row>
     <row r="11" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="120">
         <v>2</v>
       </c>
-      <c r="D11" s="131" t="s">
+      <c r="D11" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131" t="s">
+      <c r="E11" s="189"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="189"/>
+      <c r="I11" s="189" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="131"/>
+      <c r="J11" s="189"/>
       <c r="K11" s="111"/>
       <c r="L11" s="115"/>
     </row>
@@ -9881,15 +9967,15 @@
       <c r="C12" s="105">
         <v>3</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
       <c r="K12" s="1"/>
       <c r="L12" s="115"/>
     </row>
@@ -9903,57 +9989,57 @@
       <c r="C13" s="105">
         <v>4</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
       <c r="K13" s="1"/>
       <c r="L13" s="115"/>
     </row>
     <row r="14" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="123" t="s">
+      <c r="A14" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="108">
         <v>5</v>
       </c>
-      <c r="D14" s="127" t="s">
+      <c r="D14" s="160" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
       <c r="K14" s="1"/>
       <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:25" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="126"/>
+      <c r="B15" s="169"/>
       <c r="C15" s="108">
         <v>6</v>
       </c>
-      <c r="D15" s="127" t="s">
+      <c r="D15" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127" t="s">
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="127"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="1"/>
       <c r="L15" s="115"/>
     </row>
@@ -9963,17 +10049,17 @@
       <c r="C16" s="105">
         <v>7</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127" t="s">
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="127"/>
+      <c r="J16" s="160"/>
       <c r="K16" s="1"/>
       <c r="L16" s="115"/>
     </row>
@@ -9983,35 +10069,35 @@
       <c r="C17" s="120">
         <v>8</v>
       </c>
-      <c r="D17" s="129" t="s">
+      <c r="D17" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
       <c r="K17" s="111"/>
       <c r="L17" s="115"/>
     </row>
     <row r="18" spans="1:18" s="11" customFormat="1" ht="30" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="124"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="170"/>
       <c r="C18" s="120">
         <v>9</v>
       </c>
-      <c r="D18" s="129" t="s">
+      <c r="D18" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129" t="s">
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="129"/>
+      <c r="J18" s="145"/>
       <c r="K18" s="111"/>
       <c r="L18" s="115"/>
     </row>
@@ -10021,15 +10107,15 @@
       <c r="C19" s="105">
         <v>10</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
+      <c r="E19" s="160"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
+      <c r="J19" s="160"/>
       <c r="K19" s="1"/>
       <c r="L19" s="112"/>
       <c r="P19" s="11"/>
@@ -10042,15 +10128,15 @@
       <c r="C20" s="120">
         <v>11</v>
       </c>
-      <c r="D20" s="129" t="s">
+      <c r="D20" s="145" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="129"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
       <c r="K20" s="111"/>
       <c r="L20" s="112"/>
       <c r="P20" s="11"/>
@@ -10063,38 +10149,38 @@
       <c r="C21" s="120">
         <v>12</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="D21" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
       <c r="K21" s="111"/>
       <c r="L21" s="112"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" ht="69.599999999999994" customHeight="1">
+    <row r="22" spans="1:18" ht="69.650000000000006" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="42"/>
       <c r="C22" s="120">
         <v>13</v>
       </c>
-      <c r="D22" s="128" t="s">
+      <c r="D22" s="213" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="129" t="s">
+      <c r="E22" s="213"/>
+      <c r="F22" s="213"/>
+      <c r="G22" s="213"/>
+      <c r="H22" s="213"/>
+      <c r="I22" s="145" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="129"/>
+      <c r="J22" s="145"/>
       <c r="K22" s="122"/>
       <c r="L22" s="117"/>
       <c r="P22" s="11"/>
